--- a/c/Complexity_Chart.xlsx
+++ b/c/Complexity_Chart.xlsx
@@ -3,21 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Chart" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Data" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Chart" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Data" sheetId="2" r:id="rId6"/>
+    <sheet state="hidden" name="ChartData_Hidden" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="YGqKnkp1t8EatEgrJOrhlKb/j98yHFdLNSL8zDjDg6o="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t>Input Size</t>
   </si>
@@ -34,6 +30,12 @@
     <t>Quick</t>
   </si>
   <si>
+    <t>Heap</t>
+  </si>
+  <si>
+    <t>Insertion</t>
+  </si>
+  <si>
     <t>Random</t>
   </si>
   <si>
@@ -42,12 +44,27 @@
   <si>
     <t>Desc</t>
   </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Heap Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -68,11 +85,6 @@
     </font>
     <font>
       <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -81,8 +93,18 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -99,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border/>
     <border>
       <left/>
@@ -126,18 +148,8 @@
       </bottom>
     </border>
     <border>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <left/>
       <right/>
-      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -188,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -199,28 +211,43 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -254,7 +281,7 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Selection Sort</a:t>
+              <a:t>Bubble Sort</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -264,11 +291,104 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:axId val="172318167"/>
-        <c:axId val="814857230"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$E$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$E$3:$E$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$F$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$F$3:$F$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$G$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$G$3:$G$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="1611950636"/>
+        <c:axId val="1121219334"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="172318167"/>
+        <c:axId val="1611950636"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -324,26 +444,91 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="814857230"/>
+        <c:crossAx val="1121219334"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="814857230"/>
+        <c:axId val="1121219334"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="172318167"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1611950636"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="t"/>
+      <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:txPr>
         <a:bodyPr/>
@@ -375,21 +560,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="1400">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" i="0" sz="1400">
+              <a:rPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Quick Sort</a:t>
+              <a:t>Insertion Sort</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -399,11 +584,104 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:axId val="772606722"/>
-        <c:axId val="1657833818"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$Q$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$Q$3:$Q$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$R$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$R$3:$R$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$S$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$S$3:$S$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="1734691376"/>
+        <c:axId val="1673431518"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="772606722"/>
+        <c:axId val="1734691376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -416,19 +694,19 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr lvl="0">
-                  <a:defRPr b="0" i="0" sz="1000">
+                  <a:defRPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" i="0" sz="1000">
+                  <a:rPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:rPr>
                   <a:t>Input Size</a:t>
                 </a:r>
@@ -450,31 +728,96 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="900">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1657833818"/>
+        <c:crossAx val="1673431518"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1657833818"/>
+        <c:axId val="1673431518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="772606722"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1734691376"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -485,11 +828,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0" i="0" sz="900">
+            <a:defRPr b="0">
               <a:solidFill>
                 <a:srgbClr val="1A1A1A"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -510,21 +853,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="1400">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" i="0" sz="1400">
+              <a:rPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Consolidated Chart</a:t>
+              <a:t>Selection Sort</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -534,11 +877,104 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:axId val="1992562160"/>
-        <c:axId val="534561724"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$B$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$B$3:$B$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$C$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$C$3:$C$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$D$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$D$3:$D$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="1657949632"/>
+        <c:axId val="625891522"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1992562160"/>
+        <c:axId val="1657949632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -551,19 +987,19 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr lvl="0">
-                  <a:defRPr b="0" i="0" sz="1000">
+                  <a:defRPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" i="0" sz="1000">
+                  <a:rPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:rPr>
                   <a:t>Input Size</a:t>
                 </a:r>
@@ -585,31 +1021,96 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="900">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="534561724"/>
+        <c:crossAx val="625891522"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="534561724"/>
+        <c:axId val="625891522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="1992562160"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1657949632"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -620,11 +1121,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0" i="0" sz="900">
+            <a:defRPr b="0">
               <a:solidFill>
                 <a:srgbClr val="1A1A1A"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -645,21 +1146,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="1400">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" i="0" sz="1400">
+              <a:rPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Merge Sort</a:t>
+              <a:t>Quick Sort</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -669,11 +1170,104 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:axId val="1422426624"/>
-        <c:axId val="1401309962"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$K$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$K$3:$K$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$L$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$L$3:$L$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$M$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$M$3:$M$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="280139809"/>
+        <c:axId val="1335781592"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1422426624"/>
+        <c:axId val="280139809"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -686,19 +1280,19 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr lvl="0">
-                  <a:defRPr b="0" i="0" sz="1000">
+                  <a:defRPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" i="0" sz="1000">
+                  <a:rPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:rPr>
                   <a:t>Input Size</a:t>
                 </a:r>
@@ -720,31 +1314,96 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="900">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1401309962"/>
+        <c:crossAx val="1335781592"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1401309962"/>
+        <c:axId val="1335781592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="1422426624"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="280139809"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -755,11 +1414,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0" i="0" sz="900">
+            <a:defRPr b="0">
               <a:solidFill>
                 <a:srgbClr val="1A1A1A"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -780,21 +1439,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="1400">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" i="0" sz="1400">
+              <a:rPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Bubble Sort</a:t>
+              <a:t>Merge Sort</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -802,22 +1461,106 @@
       <c:overlay val="0"/>
     </c:title>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.17743193865472698"/>
-          <c:y val="0.17171296296296296"/>
-          <c:w val="0.5676985229787453"/>
-          <c:h val="0.6227161708953047"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:lineChart>
-        <c:axId val="136663068"/>
-        <c:axId val="1390389831"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$H$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$H$3:$H$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$I$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$I$3:$I$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$J$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$J$3:$J$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="754857350"/>
+        <c:axId val="393847948"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="136663068"/>
+        <c:axId val="754857350"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -830,19 +1573,19 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr lvl="0">
-                  <a:defRPr b="0" i="0" sz="1000">
+                  <a:defRPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" i="0" sz="1000">
+                  <a:rPr b="0">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="+mn-lt"/>
                   </a:rPr>
                   <a:t>Input Size</a:t>
                 </a:r>
@@ -864,31 +1607,96 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="900">
+              <a:defRPr b="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1390389831"/>
+        <c:crossAx val="393847948"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1390389831"/>
+        <c:axId val="393847948"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="136663068"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="754857350"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -899,11 +1707,690 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0" i="0" sz="900">
+            <a:defRPr b="0">
               <a:solidFill>
                 <a:srgbClr val="1A1A1A"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Heap Sort</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$N$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$N$3:$N$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$O$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$O$3:$O$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Data!$P$2</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Data!$A$3:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$P$3:$P$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="654053340"/>
+        <c:axId val="330541284"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="654053340"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Input Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="330541284"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="330541284"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="654053340"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Consolidated Chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$A$2:$A$10</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ChartData_Hidden!$B$2:$B$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$C$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$A$2:$A$10</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ChartData_Hidden!$C$2:$C$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$D$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$A$2:$A$10</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ChartData_Hidden!$D$2:$D$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$E$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$A$2:$A$10</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ChartData_Hidden!$E$2:$E$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$F$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$A$2:$A$10</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ChartData_Hidden!$F$2:$F$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$G$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>ChartData_Hidden!$A$2:$A$10</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ChartData_Hidden!$G$2:$G$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="1248737144"/>
+        <c:axId val="1244621682"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1248737144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Input Size</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1244621682"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1244621682"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Execution Time (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1248737144"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="Roboto"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -915,18 +2402,22 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:colOff>904875</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3829050" cy="2714625"/>
+    <xdr:ext cx="4286250" cy="2857500"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1830814073" name="Chart 1" title="Chart"/>
+        <xdr:cNvPr id="1" name="Chart 1" title="Bubble Sort"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -943,15 +2434,15 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4533900" cy="2743200"/>
+    <xdr:ext cx="4286250" cy="2857500"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="969654167" name="Chart 2" title="Chart"/>
+        <xdr:cNvPr id="2" name="Chart 2" title="Insertion Sort"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -968,15 +2459,15 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4533900" cy="2743200"/>
+    <xdr:ext cx="4286250" cy="2857500"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="720062503" name="Chart 3" title="Chart"/>
+        <xdr:cNvPr id="3" name="Chart 3" title="Selection Sort"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -993,15 +2484,15 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4533900" cy="2743200"/>
+    <xdr:ext cx="4286250" cy="2857500"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="686942418" name="Chart 4" title="Chart"/>
+        <xdr:cNvPr id="4" name="Chart 4" title="Quick Sort"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1018,15 +2509,15 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4419600" cy="2743200"/>
+    <xdr:ext cx="4286250" cy="2857500"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="530079624" name="Chart 5" title="Chart"/>
+        <xdr:cNvPr id="5" name="Chart 5" title="Merge Sort"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1041,11 +2532,65 @@
     </xdr:graphicFrame>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4286250" cy="2857500"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 6" title="Heap Sort"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3810000"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 7" title="Consolidated Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1251,7 +2796,7 @@
   <cols>
     <col customWidth="1" min="1" max="3" width="14.38"/>
     <col customWidth="1" min="4" max="4" width="13.75"/>
-    <col customWidth="1" min="5" max="26" width="14.38"/>
+    <col customWidth="1" min="5" max="6" width="14.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
@@ -2290,283 +3835,651 @@
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="3"/>
       <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="7" t="s">
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="7" t="s">
+      <c r="I2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
+      <c r="L2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="9">
+      <c r="A3" s="7">
         <v>0.0</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
+      <c r="B3" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="S3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>8000.0</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
+      <c r="B4" s="12">
+        <v>44.93</v>
+      </c>
+      <c r="C4" s="13">
+        <v>43.88</v>
+      </c>
+      <c r="D4" s="13">
+        <v>46.19</v>
+      </c>
+      <c r="E4" s="12">
+        <v>78.07</v>
+      </c>
+      <c r="F4" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G4" s="13">
+        <v>102.77</v>
+      </c>
+      <c r="H4" s="12">
+        <v>1.12</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0.47</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0.48</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="L4" s="13">
+        <v>130.02</v>
+      </c>
+      <c r="M4" s="13">
+        <v>82.65</v>
+      </c>
+      <c r="N4" s="12">
+        <v>1.58</v>
+      </c>
+      <c r="O4" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="P4" s="13">
+        <v>1.18</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>33.5</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="S4" s="13">
+        <v>67.26</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>12000.0</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
+      <c r="B5" s="15">
+        <v>100.92</v>
+      </c>
+      <c r="C5" s="15">
+        <v>98.41</v>
+      </c>
+      <c r="D5" s="15">
+        <v>103.79</v>
+      </c>
+      <c r="E5" s="15">
+        <v>175.15</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.02</v>
+      </c>
+      <c r="G5" s="15">
+        <v>230.49</v>
+      </c>
+      <c r="H5" s="15">
+        <v>1.74</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0.73</v>
+      </c>
+      <c r="J5" s="15">
+        <v>0.74</v>
+      </c>
+      <c r="K5" s="15">
+        <v>1.45</v>
+      </c>
+      <c r="L5" s="15">
+        <v>294.29</v>
+      </c>
+      <c r="M5" s="15">
+        <v>183.41</v>
+      </c>
+      <c r="N5" s="15">
+        <v>2.45</v>
+      </c>
+      <c r="O5" s="15">
+        <v>1.84</v>
+      </c>
+      <c r="P5" s="15">
+        <v>1.81</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>75.58</v>
+      </c>
+      <c r="R5" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="S5" s="15">
+        <v>151.85</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>16000.0</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="B6" s="15">
+        <v>177.05</v>
+      </c>
+      <c r="C6" s="15">
+        <v>174.96</v>
+      </c>
+      <c r="D6" s="15">
+        <v>184.51</v>
+      </c>
+      <c r="E6" s="15">
+        <v>315.61</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.03</v>
+      </c>
+      <c r="G6" s="15">
+        <v>409.65</v>
+      </c>
+      <c r="H6" s="15">
+        <v>2.37</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="J6" s="15">
+        <v>1.04</v>
+      </c>
+      <c r="K6" s="15">
+        <v>1.89</v>
+      </c>
+      <c r="L6" s="15">
+        <v>523.46</v>
+      </c>
+      <c r="M6" s="15">
+        <v>329.96</v>
+      </c>
+      <c r="N6" s="15">
+        <v>3.36</v>
+      </c>
+      <c r="O6" s="15">
+        <v>2.46</v>
+      </c>
+      <c r="P6" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>135.38</v>
+      </c>
+      <c r="R6" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="S6" s="15">
+        <v>270.91</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>20000.0</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
+      <c r="B7" s="15">
+        <v>278.13</v>
+      </c>
+      <c r="C7" s="15">
+        <v>273.89</v>
+      </c>
+      <c r="D7" s="15">
+        <v>288.23</v>
+      </c>
+      <c r="E7" s="15">
+        <v>486.99</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.03</v>
+      </c>
+      <c r="G7" s="15">
+        <v>639.24</v>
+      </c>
+      <c r="H7" s="15">
+        <v>3.03</v>
+      </c>
+      <c r="I7" s="15">
+        <v>1.29</v>
+      </c>
+      <c r="J7" s="15">
+        <v>1.28</v>
+      </c>
+      <c r="K7" s="15">
+        <v>2.52</v>
+      </c>
+      <c r="L7" s="15">
+        <v>764.19</v>
+      </c>
+      <c r="M7" s="15">
+        <v>515.21</v>
+      </c>
+      <c r="N7" s="15">
+        <v>4.28</v>
+      </c>
+      <c r="O7" s="15">
+        <v>3.17</v>
+      </c>
+      <c r="P7" s="15">
+        <v>3.16</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>212.18</v>
+      </c>
+      <c r="R7" s="15">
+        <v>0.06</v>
+      </c>
+      <c r="S7" s="15">
+        <v>431.26</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>24000.0</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="B8" s="15">
+        <v>398.65</v>
+      </c>
+      <c r="C8" s="15">
+        <v>393.61</v>
+      </c>
+      <c r="D8" s="15">
+        <v>415.24</v>
+      </c>
+      <c r="E8" s="15">
+        <v>710.96</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="15">
+        <v>920.02</v>
+      </c>
+      <c r="H8" s="15">
+        <v>3.69</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1.54</v>
+      </c>
+      <c r="J8" s="15">
+        <v>1.57</v>
+      </c>
+      <c r="K8" s="15">
+        <v>3.02</v>
+      </c>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="N8" s="15">
+        <v>5.24</v>
+      </c>
+      <c r="O8" s="15">
+        <v>3.82</v>
+      </c>
+      <c r="P8" s="15">
+        <v>3.85</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>302.1</v>
+      </c>
+      <c r="R8" s="15">
+        <v>0.07</v>
+      </c>
+      <c r="S8" s="15">
+        <v>610.2</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>28000.0</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
+      <c r="B9" s="15">
+        <v>542.49</v>
+      </c>
+      <c r="C9" s="15">
+        <v>535.56</v>
+      </c>
+      <c r="D9" s="15">
+        <v>564.63</v>
+      </c>
+      <c r="E9" s="15">
+        <v>973.61</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="G9" s="15">
+        <v>1254.51</v>
+      </c>
+      <c r="H9" s="15">
+        <v>4.33</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1.82</v>
+      </c>
+      <c r="J9" s="15">
+        <v>1.86</v>
+      </c>
+      <c r="K9" s="15">
+        <v>3.56</v>
+      </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
+      <c r="N9" s="15">
+        <v>6.22</v>
+      </c>
+      <c r="O9" s="15">
+        <v>4.51</v>
+      </c>
+      <c r="P9" s="15">
+        <v>4.53</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>416.78</v>
+      </c>
+      <c r="R9" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="S9" s="15">
+        <v>832.14</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>32000.0</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
+      <c r="B10" s="15">
+        <v>710.18</v>
+      </c>
+      <c r="C10" s="15">
+        <v>699.86</v>
+      </c>
+      <c r="D10" s="15">
+        <v>739.7</v>
+      </c>
+      <c r="E10" s="15">
+        <v>1259.94</v>
+      </c>
+      <c r="F10" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1638.66</v>
+      </c>
+      <c r="H10" s="15">
+        <v>5.04</v>
+      </c>
+      <c r="I10" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="J10" s="15">
+        <v>2.15</v>
+      </c>
+      <c r="K10" s="15">
+        <v>4.09</v>
+      </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
+      <c r="N10" s="15">
+        <v>7.2</v>
+      </c>
+      <c r="O10" s="15">
+        <v>5.17</v>
+      </c>
+      <c r="P10" s="15">
+        <v>5.18</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>547.53</v>
+      </c>
+      <c r="R10" s="15">
+        <v>0.09</v>
+      </c>
+      <c r="S10" s="15">
+        <v>1098.55</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>36000.0</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
+      <c r="B11" s="15">
+        <v>898.35</v>
+      </c>
+      <c r="C11" s="15">
+        <v>886.09</v>
+      </c>
+      <c r="D11" s="15">
+        <v>936.45</v>
+      </c>
+      <c r="E11" s="15">
+        <v>1590.54</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.06</v>
+      </c>
+      <c r="G11" s="15">
+        <v>2075.97</v>
+      </c>
+      <c r="H11" s="15">
+        <v>5.72</v>
+      </c>
+      <c r="I11" s="15">
+        <v>2.41</v>
+      </c>
+      <c r="J11" s="15">
+        <v>2.42</v>
+      </c>
+      <c r="K11" s="15">
+        <v>4.78</v>
+      </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
+      <c r="N11" s="15">
+        <v>8.2</v>
+      </c>
+      <c r="O11" s="15">
+        <v>5.83</v>
+      </c>
+      <c r="P11" s="15">
+        <v>5.94</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>688.83</v>
+      </c>
+      <c r="R11" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="S11" s="15">
+        <v>1377.4</v>
+      </c>
     </row>
     <row r="12" ht="9.0" customHeight="1">
-      <c r="M12" s="8"/>
+      <c r="M12" s="17"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="M13" s="8"/>
+      <c r="M13" s="17"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="F14" s="8"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="F15" s="8"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="F16" s="8"/>
+      <c r="F16" s="17"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="D17" s="11"/>
-      <c r="F17" s="8"/>
+      <c r="D17" s="18"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="D18" s="11"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="D19" s="11"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="D20" s="11"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="D21" s="11"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="D22" s="11"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="D23" s="11"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="D24" s="11"/>
+      <c r="D24" s="18"/>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
@@ -3545,16 +5458,324 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="str">
+        <f>Data!A1</f>
+        <v>Input Size</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20">
+        <f>Data!A3</f>
+        <v>0</v>
+      </c>
+      <c r="B2" s="20">
+        <f>Data!B3</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="20">
+        <f>Data!E3</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="20">
+        <f>Data!H3</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="20">
+        <f>Data!K3</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="20">
+        <f>Data!N3</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="20">
+        <f>Data!Q3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20">
+        <f>Data!A4</f>
+        <v>8000</v>
+      </c>
+      <c r="B3" s="20">
+        <f>Data!B4</f>
+        <v>44.93</v>
+      </c>
+      <c r="C3" s="20">
+        <f>Data!E4</f>
+        <v>78.07</v>
+      </c>
+      <c r="D3" s="20">
+        <f>Data!H4</f>
+        <v>1.12</v>
+      </c>
+      <c r="E3" s="20">
+        <f>Data!K4</f>
+        <v>0.93</v>
+      </c>
+      <c r="F3" s="20">
+        <f>Data!N4</f>
+        <v>1.58</v>
+      </c>
+      <c r="G3" s="20">
+        <f>Data!Q4</f>
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20">
+        <f>Data!A5</f>
+        <v>12000</v>
+      </c>
+      <c r="B4" s="20">
+        <f>Data!B5</f>
+        <v>100.92</v>
+      </c>
+      <c r="C4" s="20">
+        <f>Data!E5</f>
+        <v>175.15</v>
+      </c>
+      <c r="D4" s="20">
+        <f>Data!H5</f>
+        <v>1.74</v>
+      </c>
+      <c r="E4" s="20">
+        <f>Data!K5</f>
+        <v>1.45</v>
+      </c>
+      <c r="F4" s="20">
+        <f>Data!N5</f>
+        <v>2.45</v>
+      </c>
+      <c r="G4" s="20">
+        <f>Data!Q5</f>
+        <v>75.58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20">
+        <f>Data!A6</f>
+        <v>16000</v>
+      </c>
+      <c r="B5" s="20">
+        <f>Data!B6</f>
+        <v>177.05</v>
+      </c>
+      <c r="C5" s="20">
+        <f>Data!E6</f>
+        <v>315.61</v>
+      </c>
+      <c r="D5" s="20">
+        <f>Data!H6</f>
+        <v>2.37</v>
+      </c>
+      <c r="E5" s="20">
+        <f>Data!K6</f>
+        <v>1.89</v>
+      </c>
+      <c r="F5" s="20">
+        <f>Data!N6</f>
+        <v>3.36</v>
+      </c>
+      <c r="G5" s="20">
+        <f>Data!Q6</f>
+        <v>135.38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20">
+        <f>Data!A7</f>
+        <v>20000</v>
+      </c>
+      <c r="B6" s="20">
+        <f>Data!B7</f>
+        <v>278.13</v>
+      </c>
+      <c r="C6" s="20">
+        <f>Data!E7</f>
+        <v>486.99</v>
+      </c>
+      <c r="D6" s="20">
+        <f>Data!H7</f>
+        <v>3.03</v>
+      </c>
+      <c r="E6" s="20">
+        <f>Data!K7</f>
+        <v>2.52</v>
+      </c>
+      <c r="F6" s="20">
+        <f>Data!N7</f>
+        <v>4.28</v>
+      </c>
+      <c r="G6" s="20">
+        <f>Data!Q7</f>
+        <v>212.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20">
+        <f>Data!A8</f>
+        <v>24000</v>
+      </c>
+      <c r="B7" s="20">
+        <f>Data!B8</f>
+        <v>398.65</v>
+      </c>
+      <c r="C7" s="20">
+        <f>Data!E8</f>
+        <v>710.96</v>
+      </c>
+      <c r="D7" s="20">
+        <f>Data!H8</f>
+        <v>3.69</v>
+      </c>
+      <c r="E7" s="20">
+        <f>Data!K8</f>
+        <v>3.02</v>
+      </c>
+      <c r="F7" s="20">
+        <f>Data!N8</f>
+        <v>5.24</v>
+      </c>
+      <c r="G7" s="20">
+        <f>Data!Q8</f>
+        <v>302.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20">
+        <f>Data!A9</f>
+        <v>28000</v>
+      </c>
+      <c r="B8" s="20">
+        <f>Data!B9</f>
+        <v>542.49</v>
+      </c>
+      <c r="C8" s="20">
+        <f>Data!E9</f>
+        <v>973.61</v>
+      </c>
+      <c r="D8" s="20">
+        <f>Data!H9</f>
+        <v>4.33</v>
+      </c>
+      <c r="E8" s="20">
+        <f>Data!K9</f>
+        <v>3.56</v>
+      </c>
+      <c r="F8" s="20">
+        <f>Data!N9</f>
+        <v>6.22</v>
+      </c>
+      <c r="G8" s="20">
+        <f>Data!Q9</f>
+        <v>416.78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20">
+        <f>Data!A10</f>
+        <v>32000</v>
+      </c>
+      <c r="B9" s="20">
+        <f>Data!B10</f>
+        <v>710.18</v>
+      </c>
+      <c r="C9" s="20">
+        <f>Data!E10</f>
+        <v>1259.94</v>
+      </c>
+      <c r="D9" s="20">
+        <f>Data!H10</f>
+        <v>5.04</v>
+      </c>
+      <c r="E9" s="20">
+        <f>Data!K10</f>
+        <v>4.09</v>
+      </c>
+      <c r="F9" s="20">
+        <f>Data!N10</f>
+        <v>7.2</v>
+      </c>
+      <c r="G9" s="20">
+        <f>Data!Q10</f>
+        <v>547.53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20">
+        <f>Data!A11</f>
+        <v>36000</v>
+      </c>
+      <c r="B10" s="20">
+        <f>Data!B11</f>
+        <v>898.35</v>
+      </c>
+      <c r="C10" s="20">
+        <f>Data!E11</f>
+        <v>1590.54</v>
+      </c>
+      <c r="D10" s="20">
+        <f>Data!H11</f>
+        <v>5.72</v>
+      </c>
+      <c r="E10" s="20">
+        <f>Data!K11</f>
+        <v>4.78</v>
+      </c>
+      <c r="F10" s="20">
+        <f>Data!N11</f>
+        <v>8.2</v>
+      </c>
+      <c r="G10" s="20">
+        <f>Data!Q11</f>
+        <v>688.83</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>